--- a/Opintosuunnitelmat.xlsx
+++ b/Opintosuunnitelmat.xlsx
@@ -88,7 +88,7 @@
     <t>Järjestelmätuessa toimiminen</t>
   </si>
   <si>
-    <t>Ilmoittaudu väylälle. Pyydä tehtävät opettajalta (Damien Kuosmanen)</t>
+    <t>Ilmoittaudu väylälle. Pyydä tehtävät opettajalta (vastuuopettaja)</t>
   </si>
   <si>
     <t>Tietoteknisen ratkaisun myynti</t>
@@ -103,7 +103,7 @@
     <t>Äidinkieli / S2</t>
   </si>
   <si>
-    <t>Avoin (Päivi Honkala)</t>
+    <t>Avoin (vastuuopettaja)</t>
   </si>
   <si>
     <t>Ruotsi</t>
@@ -157,37 +157,37 @@
     <t>Unix-komentorivin perusteet (valinnainen)</t>
   </si>
   <si>
-    <t>Joustava (Edward Krogius)</t>
+    <t>Joustava (vastuuopettaja)</t>
   </si>
   <si>
     <t>Tulee osana tieto- ja viestintätekniikan perustehtäviä</t>
   </si>
   <si>
-    <t>Joustava (Elina Kuutti)</t>
-  </si>
-  <si>
-    <t>Avoin (Mika Kurki)</t>
-  </si>
-  <si>
-    <t>Joustava (Matti Seise / Antti Honkasalo)</t>
-  </si>
-  <si>
-    <t>Avoin (Petteri Kärkkäinen)</t>
+    <t>Joustava (vastuuopettaja)</t>
+  </si>
+  <si>
+    <t>Avoin (vastuuopettaja)</t>
+  </si>
+  <si>
+    <t>Joustava (vastuuopettaja)</t>
+  </si>
+  <si>
+    <t>Avoin (vastuuopettaja)</t>
   </si>
   <si>
     <t>Lukio-opintojen suorittaminen TYK:issä</t>
   </si>
   <si>
-    <t>Avoin 2018 PAK Yhteiskunnassa ja kansalaisena toimiminen (Piritta Pyykönen)</t>
-  </si>
-  <si>
-    <t>Avoin 2020 PAK Yrittäjyys ja yrittäjämäinen toiminta (Piritta Pyykönen)</t>
-  </si>
-  <si>
-    <t>Avoin 2018 PAK Työkyvyn ja hyvinvoinnin ylläpit., terveystieto &amp; Avoin 2018 PAK Työkyvyn ja hyvinvoinnin ylläpitäminen, liikunta (Petteri Kärkkäinen)</t>
-  </si>
-  <si>
-    <t>Avoin 2018 PAK Kestävän kehityksen edistäminen, pakollinen (Tuomas Kalliokoski)</t>
+    <t>Avoin 2018 PAK Yhteiskunnassa ja kansalaisena toimiminen (vastuuopettaja)</t>
+  </si>
+  <si>
+    <t>Avoin 2020 PAK Yrittäjyys ja yrittäjämäinen toiminta (vastuuopettaja)</t>
+  </si>
+  <si>
+    <t>Avoin 2018 PAK Työkyvyn ja hyvinvoinnin ylläpit., terveystieto &amp; Avoin 2018 PAK Työkyvyn ja hyvinvoinnin ylläpitäminen, liikunta (vastuuopettaja)</t>
+  </si>
+  <si>
+    <t>Avoin 2018 PAK Kestävän kehityksen edistäminen, pakollinen (vastuuopettaja)</t>
   </si>
 </sst>
 </file>
